--- a/templates/04_Avg_Ticket_Template.xlsx
+++ b/templates/04_Avg_Ticket_Template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avg Ticket" sheetId="1" r:id="R17ae8f15fa26483b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avg Ticket" sheetId="1" r:id="R49474a018c3c43e3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -812,7 +812,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="7" t="str">
-        <x:v>Yo-Chi Charlestown</x:v>
+        <x:v>Yo-Chi Chatswood</x:v>
       </x:c>
       <x:c r="B15" s="8" t="n">
         <x:v>12.5</x:v>
@@ -853,7 +853,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="7" t="str">
-        <x:v>Yo-Chi Chatswood</x:v>
+        <x:v>Yo-Chi Chevron Surfers Paradise</x:v>
       </x:c>
       <x:c r="B16" s="8" t="n">
         <x:v>12.5</x:v>
@@ -894,7 +894,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="7" t="str">
-        <x:v>Yo-Chi Chevron Surfers Paradise</x:v>
+        <x:v>Yo-Chi Chippendale</x:v>
       </x:c>
       <x:c r="B17" s="8" t="n">
         <x:v>12.5</x:v>
@@ -935,7 +935,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="7" t="str">
-        <x:v>Yo-Chi Chippendale</x:v>
+        <x:v>Yo-Chi Circular Quay</x:v>
       </x:c>
       <x:c r="B18" s="8" t="n">
         <x:v>12.5</x:v>
@@ -976,7 +976,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="7" t="str">
-        <x:v>Yo-Chi Circular Quay</x:v>
+        <x:v>Yo-Chi Claremont</x:v>
       </x:c>
       <x:c r="B19" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1017,7 +1017,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="7" t="str">
-        <x:v>Yo-Chi Claremont</x:v>
+        <x:v>Yo-Chi Cockburn Central</x:v>
       </x:c>
       <x:c r="B20" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1058,7 +1058,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="7" t="str">
-        <x:v>Yo-Chi Cockburn Central</x:v>
+        <x:v>Yo-Chi Coogee</x:v>
       </x:c>
       <x:c r="B21" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1099,7 +1099,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="7" t="str">
-        <x:v>Yo-Chi Coogee</x:v>
+        <x:v>Yo-Chi Cronulla</x:v>
       </x:c>
       <x:c r="B22" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1140,7 +1140,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="7" t="str">
-        <x:v>Yo-Chi Cronulla</x:v>
+        <x:v>Yo-Chi Currambine</x:v>
       </x:c>
       <x:c r="B23" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1181,7 +1181,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="7" t="str">
-        <x:v>Yo-Chi Currambine</x:v>
+        <x:v>Yo-Chi Double Bay</x:v>
       </x:c>
       <x:c r="B24" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1222,7 +1222,7 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="7" t="str">
-        <x:v>Yo-Chi Double Bay</x:v>
+        <x:v>Yo-Chi Eastland</x:v>
       </x:c>
       <x:c r="B25" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1263,7 +1263,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="7" t="str">
-        <x:v>Yo-Chi Eastland</x:v>
+        <x:v>Yo-Chi Forrest Chase</x:v>
       </x:c>
       <x:c r="B26" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1304,7 +1304,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="7" t="str">
-        <x:v>Yo-Chi Forrest Chase</x:v>
+        <x:v>Yo-Chi Fremantle</x:v>
       </x:c>
       <x:c r="B27" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1345,7 +1345,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="7" t="str">
-        <x:v>Yo-Chi Fremantle</x:v>
+        <x:v>Yo-Chi Gasworks</x:v>
       </x:c>
       <x:c r="B28" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1386,7 +1386,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="7" t="str">
-        <x:v>Yo-Chi Gasworks</x:v>
+        <x:v>Yo-Chi George St</x:v>
       </x:c>
       <x:c r="B29" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1427,7 +1427,7 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="7" t="str">
-        <x:v>Yo-Chi George St</x:v>
+        <x:v>Yo-Chi Glenelg</x:v>
       </x:c>
       <x:c r="B30" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1468,7 +1468,7 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="7" t="str">
-        <x:v>Yo-Chi Glenelg</x:v>
+        <x:v>Yo-Chi Gouger St</x:v>
       </x:c>
       <x:c r="B31" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1509,7 +1509,7 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="7" t="str">
-        <x:v>Yo-Chi Gouger St</x:v>
+        <x:v>Yo-Chi Harbour Town</x:v>
       </x:c>
       <x:c r="B32" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1550,7 +1550,7 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="7" t="str">
-        <x:v>Yo-Chi Harbour Town</x:v>
+        <x:v>Yo-Chi Hawthorn</x:v>
       </x:c>
       <x:c r="B33" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1591,7 +1591,7 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="7" t="str">
-        <x:v>Yo-Chi Hawthorn</x:v>
+        <x:v>Yo-Chi Henley Beach</x:v>
       </x:c>
       <x:c r="B34" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1632,7 +1632,7 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="7" t="str">
-        <x:v>Yo-Chi Henley Beach</x:v>
+        <x:v>Yo-Chi Highgate</x:v>
       </x:c>
       <x:c r="B35" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1673,7 +1673,7 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="7" t="str">
-        <x:v>Yo-Chi Highgate</x:v>
+        <x:v>Yo-Chi Highpoint</x:v>
       </x:c>
       <x:c r="B36" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1714,7 +1714,7 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="7" t="str">
-        <x:v>Yo-Chi Highpoint</x:v>
+        <x:v>Yo-Chi Indooroopilly</x:v>
       </x:c>
       <x:c r="B37" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1755,7 +1755,7 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="7" t="str">
-        <x:v>Yo-Chi Indooroopilly</x:v>
+        <x:v>Yo-Chi Karrinyup</x:v>
       </x:c>
       <x:c r="B38" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1796,7 +1796,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="7" t="str">
-        <x:v>Yo-Chi Karrinyup</x:v>
+        <x:v>Yo-Chi Kawana Waters</x:v>
       </x:c>
       <x:c r="B39" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1837,7 +1837,7 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="7" t="str">
-        <x:v>Yo-Chi Kawana Waters</x:v>
+        <x:v>Yo-Chi Lane Cove</x:v>
       </x:c>
       <x:c r="B40" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1878,7 +1878,7 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="7" t="str">
-        <x:v>Yo-Chi Lane Cove</x:v>
+        <x:v>Yo-Chi Leederville</x:v>
       </x:c>
       <x:c r="B41" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1919,7 +1919,7 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="7" t="str">
-        <x:v>Yo-Chi Leederville</x:v>
+        <x:v>Yo-Chi Macquarie</x:v>
       </x:c>
       <x:c r="B42" s="8" t="n">
         <x:v>12.5</x:v>
@@ -1960,7 +1960,7 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="7" t="str">
-        <x:v>Yo-Chi Macquarie</x:v>
+        <x:v>Yo-Chi Malvern</x:v>
       </x:c>
       <x:c r="B43" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2001,7 +2001,7 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="7" t="str">
-        <x:v>Yo-Chi Malvern</x:v>
+        <x:v>Yo-Chi Mandurah</x:v>
       </x:c>
       <x:c r="B44" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2042,7 +2042,7 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="7" t="str">
-        <x:v>Yo-Chi Mandurah</x:v>
+        <x:v>Yo-Chi Manly</x:v>
       </x:c>
       <x:c r="B45" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2083,7 +2083,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="7" t="str">
-        <x:v>Yo-Chi Manly</x:v>
+        <x:v>Yo-Chi Mt Gravatt</x:v>
       </x:c>
       <x:c r="B46" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2124,7 +2124,7 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="7" t="str">
-        <x:v>Yo-Chi Mt Gravatt</x:v>
+        <x:v>Yo-Chi Newtown</x:v>
       </x:c>
       <x:c r="B47" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2165,7 +2165,7 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="7" t="str">
-        <x:v>Yo-Chi Newtown</x:v>
+        <x:v>Yo-Chi Noosa</x:v>
       </x:c>
       <x:c r="B48" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2206,7 +2206,7 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="7" t="str">
-        <x:v>Yo-Chi Noosa</x:v>
+        <x:v>Yo-Chi Norwood</x:v>
       </x:c>
       <x:c r="B49" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2247,7 +2247,7 @@
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="7" t="str">
-        <x:v>Yo-Chi Norwood</x:v>
+        <x:v>Yo-Chi Paddington</x:v>
       </x:c>
       <x:c r="B50" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2288,7 +2288,7 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="7" t="str">
-        <x:v>Yo-Chi Paddington</x:v>
+        <x:v>Yo-Chi Penrith</x:v>
       </x:c>
       <x:c r="B51" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2329,7 +2329,7 @@
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="7" t="str">
-        <x:v>Yo-Chi Penrith</x:v>
+        <x:v>Yo-Chi Prospect</x:v>
       </x:c>
       <x:c r="B52" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2370,7 +2370,7 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="7" t="str">
-        <x:v>Yo-Chi Prospect</x:v>
+        <x:v>Yo-Chi QV</x:v>
       </x:c>
       <x:c r="B53" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2411,7 +2411,7 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="7" t="str">
-        <x:v>Yo-Chi QV</x:v>
+        <x:v>Yo-Chi Randwick</x:v>
       </x:c>
       <x:c r="B54" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2452,7 +2452,7 @@
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="7" t="str">
-        <x:v>Yo-Chi Randwick</x:v>
+        <x:v>Yo-Chi Robina</x:v>
       </x:c>
       <x:c r="B55" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2493,7 +2493,7 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="7" t="str">
-        <x:v>Yo-Chi Robina</x:v>
+        <x:v>Yo-Chi Rouse Hill</x:v>
       </x:c>
       <x:c r="B56" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2534,7 +2534,7 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="7" t="str">
-        <x:v>Yo-Chi Rouse Hill</x:v>
+        <x:v>Yo-Chi Semaphore</x:v>
       </x:c>
       <x:c r="B57" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2575,7 +2575,7 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="7" t="str">
-        <x:v>Yo-Chi Semaphore</x:v>
+        <x:v>Yo-Chi South Perth</x:v>
       </x:c>
       <x:c r="B58" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2616,7 +2616,7 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="7" t="str">
-        <x:v>Yo-Chi South Perth</x:v>
+        <x:v>Yo-Chi Southbank</x:v>
       </x:c>
       <x:c r="B59" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2657,7 +2657,7 @@
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="7" t="str">
-        <x:v>Yo-Chi Southbank</x:v>
+        <x:v>Yo-Chi Southland</x:v>
       </x:c>
       <x:c r="B60" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2698,7 +2698,7 @@
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="7" t="str">
-        <x:v>Yo-Chi Southland</x:v>
+        <x:v>Yo-Chi Sunshine Plaza</x:v>
       </x:c>
       <x:c r="B61" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2739,7 +2739,7 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="7" t="str">
-        <x:v>Yo-Chi Sunshine Plaza</x:v>
+        <x:v>Yo-Chi Surry Hills</x:v>
       </x:c>
       <x:c r="B62" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2780,7 +2780,7 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="7" t="str">
-        <x:v>Yo-Chi Surry Hills</x:v>
+        <x:v>Yo-Chi Tea Tree Plaza</x:v>
       </x:c>
       <x:c r="B63" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2821,7 +2821,7 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="7" t="str">
-        <x:v>Yo-Chi Tea Tree Plaza</x:v>
+        <x:v>Yo-Chi The Esplanade Surfers Paradise</x:v>
       </x:c>
       <x:c r="B64" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2862,7 +2862,7 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="7" t="str">
-        <x:v>Yo-Chi The Esplanade Surfers Paradise</x:v>
+        <x:v>Yo-Chi Top Ryde</x:v>
       </x:c>
       <x:c r="B65" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2903,7 +2903,7 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="7" t="str">
-        <x:v>Yo-Chi Top Ryde</x:v>
+        <x:v>Yo-Chi Vic Park</x:v>
       </x:c>
       <x:c r="B66" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2944,7 +2944,7 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="7" t="str">
-        <x:v>Yo-Chi Vic Park</x:v>
+        <x:v>Yo-Chi West End</x:v>
       </x:c>
       <x:c r="B67" s="8" t="n">
         <x:v>12.5</x:v>
@@ -2985,7 +2985,7 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="7" t="str">
-        <x:v>Yo-Chi West End</x:v>
+        <x:v>Yo-Chi Whitford City</x:v>
       </x:c>
       <x:c r="B68" s="8" t="n">
         <x:v>12.5</x:v>
@@ -3026,7 +3026,7 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="7" t="str">
-        <x:v>Yo-Chi Whitford City</x:v>
+        <x:v>Yo-Chi Windsor</x:v>
       </x:c>
       <x:c r="B69" s="8" t="n">
         <x:v>12.5</x:v>
@@ -3062,47 +3062,6 @@
         <x:v>12.5</x:v>
       </x:c>
       <x:c r="M69" s="8" t="n">
-        <x:v>12.5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70">
-      <x:c r="A70" s="7" t="str">
-        <x:v>Yo-Chi Windsor</x:v>
-      </x:c>
-      <x:c r="B70" s="8" t="n">
-        <x:v>12.5</x:v>
-      </x:c>
-      <x:c r="C70" s="8" t="n">
-        <x:v>12.5</x:v>
-      </x:c>
-      <x:c r="D70" s="8" t="n">
-        <x:v>12.5</x:v>
-      </x:c>
-      <x:c r="E70" s="8" t="n">
-        <x:v>12.5</x:v>
-      </x:c>
-      <x:c r="F70" s="8" t="n">
-        <x:v>12.5</x:v>
-      </x:c>
-      <x:c r="G70" s="8" t="n">
-        <x:v>12.5</x:v>
-      </x:c>
-      <x:c r="H70" s="8" t="n">
-        <x:v>12.5</x:v>
-      </x:c>
-      <x:c r="I70" s="8" t="n">
-        <x:v>12.5</x:v>
-      </x:c>
-      <x:c r="J70" s="8" t="n">
-        <x:v>12.5</x:v>
-      </x:c>
-      <x:c r="K70" s="8" t="n">
-        <x:v>12.5</x:v>
-      </x:c>
-      <x:c r="L70" s="8" t="n">
-        <x:v>12.5</x:v>
-      </x:c>
-      <x:c r="M70" s="8" t="n">
         <x:v>12.5</x:v>
       </x:c>
     </x:row>
